--- a/e2e/downloadedFile/tunjangan_jabatan_2_Q1.xlsx
+++ b/e2e/downloadedFile/tunjangan_jabatan_2_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -62,9 +62,6 @@
     <t>II</t>
   </si>
   <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
     <t>121,00</t>
   </si>
   <si>
@@ -101,13 +98,19 @@
     <t>18,00</t>
   </si>
   <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>400,00</t>
+  </si>
+  <si>
     <t>GRAND TOTAL</t>
   </si>
   <si>
-    <t>439,00</t>
-  </si>
-  <si>
-    <t>DILI, 14 August 2026</t>
+    <t>839,00</t>
+  </si>
+  <si>
+    <t>DILI, 18 August 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -224,7 +227,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="514350" cy="333375"/>
@@ -543,13 +546,13 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
     <col min="2" max="2" width="31.707" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -627,23 +630,21 @@
       <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -651,130 +652,157 @@
         <v>92003</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3">
+        <v>74003</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12"/>
+      <c r="A12"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5" t="s">
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D14"/>
-      <c r="G14" t="s">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" customHeight="1" ht="37.5">
-      <c r="A15"/>
       <c r="D15"/>
-      <c r="G15"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="1" t="s">
+      <c r="G15" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="16" spans="1:9" customHeight="1" ht="37.5">
+      <c r="A16"/>
       <c r="D16"/>
-      <c r="G16" s="1" t="s">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
+      <c r="D17"/>
+      <c r="G17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D17"/>
-      <c r="G17" t="s">
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
         <v>38</v>
+      </c>
+      <c r="D18"/>
+      <c r="G18" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -790,15 +818,12 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:I14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G15:I15"/>
@@ -808,6 +833,9 @@
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="G17:I17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
